--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110557</v>
+        <v>110562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110562</v>
+        <v>110655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110655</v>
+        <v>110681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,6 +780,131 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127919571</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>I 609, 622 52 Gotlands kommun, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>714259</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6385475</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hörsne</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110681</v>
+        <v>110694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110694</v>
+        <v>110703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110703</v>
+        <v>110708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127919571</v>
       </c>
       <c r="B3" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110708</v>
+        <v>110736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110736</v>
+        <v>110749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127919571</v>
       </c>
       <c r="B3" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128328261</v>
       </c>
       <c r="B2" t="n">
-        <v>110749</v>
+        <v>110753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127919571</v>
       </c>
       <c r="B3" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2023 artfynd.xlsx
+++ b/artfynd/A 13627-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127919571</v>
       </c>
       <c r="B3" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
